--- a/resources/templates/standard/L1100-02.xlsx
+++ b/resources/templates/standard/L1100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>설비 제작진행 체크 리스트</t>
   </si>
@@ -588,12 +591,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -637,7 +642,7 @@
     </row>
     <row r="3" ht="20.15" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -655,7 +660,7 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
@@ -664,7 +669,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -673,7 +678,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="11"/>
@@ -684,7 +689,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
@@ -693,7 +698,7 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -702,7 +707,7 @@
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
       <c r="H5" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="11"/>
@@ -713,7 +718,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="14"/>
@@ -722,7 +727,7 @@
     </row>
     <row r="6" ht="20.15" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
